--- a/static/templates/budget_bulkupdate.xlsx
+++ b/static/templates/budget_bulkupdate.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kantor\Semangat Waja Tama\Proyek\PMIS\PMIS_SWT\media\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kantor\Semangat Waja Tama\Proyek\PMIS\PMIS_SWT\static\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF2B741-5658-44CE-A22A-13A9C5C8216E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF2A44B-A76B-4606-BF69-E868DCACE3E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1464" yWindow="1464" windowWidth="17280" windowHeight="8904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>Cost Code</t>
   </si>
@@ -56,14 +56,29 @@
     <t>1. JANGAN UBAH STRUKTUR KOLOM TABEL</t>
   </si>
   <si>
-    <t>2. Isi Kolom Pada tabel sebelah Kanan</t>
+    <t>2. Isi Kolom Pada tabel sebelah Kiri</t>
+  </si>
+  <si>
+    <t>Contoh Pengisian</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>Sewa Mess Pekerja</t>
+  </si>
+  <si>
+    <t>Untuk sewa mess pekerja 7 kamar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -79,16 +94,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -96,15 +124,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -383,10 +433,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="12" max="12" width="14.89453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.26171875" customWidth="1"/>
+    <col min="16" max="16" width="12.26171875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="27.734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -402,19 +458,47 @@
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="1"/>
+      <c r="N2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="P2" s="6">
+        <v>7000000</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>